--- a/tests/agent_contract/data/M2_employee_performance.xlsx
+++ b/tests/agent_contract/data/M2_employee_performance.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绩效数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工绩效" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,2018 +413,1736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>员工ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>绩效分数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>员工ID</t>
-        </is>
+      <c r="A2" t="n">
+        <v>10001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>员工10001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>客户数</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>投诉次数</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>考勤天数</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>员工10001</t>
+          <t>员工10002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11197</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>20</v>
+        <v>86</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>员工10002</t>
+          <t>员工10003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10655</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>21</v>
+        <v>88</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10003</v>
+        <v>10004</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>员工10003</t>
+          <t>员工10004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20867</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>21</v>
+        <v>87</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10004</v>
+        <v>10005</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>员工10004</t>
+          <t>员工10005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17124</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>22</v>
+        <v>72</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10005</v>
+        <v>10006</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>员工10005</t>
+          <t>员工10006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22792</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>20</v>
+        <v>71</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10006</v>
+        <v>10007</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>员工10006</t>
+          <t>员工10007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16370</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20</v>
+        <v>97</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10007</v>
+        <v>10008</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>员工10007</t>
+          <t>员工10008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21827</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>21</v>
+        <v>78</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10008</v>
+        <v>10009</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>员工10008</t>
+          <t>员工10009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21232</v>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20</v>
+        <v>98</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10009</v>
+        <v>10010</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>员工10009</t>
+          <t>员工10010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22574</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>21</v>
+        <v>65</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10010</v>
+        <v>10011</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>员工10010</t>
+          <t>员工10011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20752</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>22</v>
+        <v>60</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10011</v>
+        <v>10012</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>员工10011</t>
+          <t>员工10012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16480</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20</v>
+        <v>99</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10012</v>
+        <v>10013</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>员工10012</t>
+          <t>员工10013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18153</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>21</v>
+        <v>64</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>员工10013</t>
+          <t>员工10014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21072</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>20</v>
+        <v>78</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10014</v>
+        <v>10015</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>员工10014</t>
+          <t>员工10015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13520</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10015</v>
+        <v>10016</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>员工10015</t>
+          <t>员工10016</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>21878</v>
-      </c>
-      <c r="E17" t="n">
-        <v>13</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>22</v>
+        <v>78</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10016</v>
+        <v>10017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>员工10016</t>
+          <t>员工10017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28878</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>21</v>
+        <v>85</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10017</v>
+        <v>10018</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>员工10017</t>
+          <t>员工10018</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19056</v>
-      </c>
-      <c r="E19" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>21</v>
+        <v>86</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10018</v>
+        <v>10019</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>员工10018</t>
+          <t>员工10019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19154</v>
-      </c>
-      <c r="E20" t="n">
-        <v>13</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>21</v>
+        <v>78</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10019</v>
+        <v>10020</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>员工10019</t>
+          <t>员工10020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24937</v>
-      </c>
-      <c r="E21" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>20</v>
+        <v>87</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10020</v>
+        <v>10021</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>员工10020</t>
+          <t>员工10021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21118</v>
-      </c>
-      <c r="E22" t="n">
-        <v>13</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>20</v>
+        <v>95</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10021</v>
+        <v>10022</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>员工10021</t>
+          <t>员工10022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60364</v>
-      </c>
-      <c r="E23" t="n">
-        <v>43</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>21</v>
+        <v>80</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10022</v>
+        <v>10023</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>员工10022</t>
+          <t>员工10023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16060</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>20</v>
+        <v>90</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10023</v>
+        <v>10024</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>员工10023</t>
+          <t>员工10024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21113</v>
-      </c>
-      <c r="E25" t="n">
-        <v>7</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>22</v>
+        <v>76</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10024</v>
+        <v>10025</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>员工10024</t>
+          <t>员工10025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13856</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>22</v>
+        <v>70</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10025</v>
+        <v>10026</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>员工10025</t>
+          <t>员工10026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15860</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>21</v>
+        <v>77</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10026</v>
+        <v>10027</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>员工10026</t>
+          <t>员工10027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11795</v>
-      </c>
-      <c r="E28" t="n">
-        <v>9</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>21</v>
+        <v>79</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10027</v>
+        <v>10028</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>员工10027</t>
+          <t>员工10028</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20884</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>22</v>
+        <v>71</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10028</v>
+        <v>10029</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>员工10028</t>
+          <t>员工10029</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>22633</v>
-      </c>
-      <c r="E30" t="n">
-        <v>7</v>
-      </c>
-      <c r="F30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" t="n">
-        <v>21</v>
+        <v>74</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10029</v>
+        <v>10030</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>员工10029</t>
+          <t>员工10030</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20388</v>
-      </c>
-      <c r="E31" t="n">
-        <v>9</v>
-      </c>
-      <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="n">
-        <v>21</v>
+        <v>79</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>10030</v>
+        <v>10031</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>员工10030</t>
+          <t>员工10031</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>21391</v>
-      </c>
-      <c r="E32" t="n">
-        <v>8</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>22</v>
+        <v>75</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10031</v>
+        <v>10032</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>员工10031</t>
+          <t>员工10032</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>18368</v>
-      </c>
-      <c r="E33" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>20</v>
+        <v>86</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>10032</v>
+        <v>10033</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>员工10032</t>
+          <t>员工10033</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10084</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>22</v>
+        <v>98</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10033</v>
+        <v>10034</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>员工10033</t>
+          <t>员工10034</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>17813</v>
-      </c>
-      <c r="E35" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>20</v>
+        <v>79</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10034</v>
+        <v>10035</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>员工10034</t>
+          <t>员工10035</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19164</v>
-      </c>
-      <c r="E36" t="n">
-        <v>11</v>
-      </c>
-      <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>22</v>
+        <v>95</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>10035</v>
+        <v>10036</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>员工10035</t>
+          <t>员工10036</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>21762</v>
-      </c>
-      <c r="E37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>21</v>
+        <v>74</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>10036</v>
+        <v>10037</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>员工10036</t>
+          <t>员工10037</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13154</v>
-      </c>
-      <c r="E38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>22</v>
+        <v>62</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10037</v>
+        <v>10038</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>员工10037</t>
+          <t>员工10038</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>研发部</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14845</v>
-      </c>
-      <c r="E39" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>21</v>
+        <v>70</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10038</v>
+        <v>10039</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>员工10038</t>
+          <t>员工10039</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25821</v>
-      </c>
-      <c r="E40" t="n">
-        <v>8</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>21</v>
+        <v>98</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10039</v>
+        <v>10040</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>员工10039</t>
+          <t>员工10040</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>75009</v>
-      </c>
-      <c r="E41" t="n">
-        <v>31</v>
-      </c>
-      <c r="F41" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>21</v>
+        <v>100</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10040</v>
+        <v>10041</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>员工10040</t>
+          <t>员工10041</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15157</v>
-      </c>
-      <c r="E42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>20</v>
+        <v>61</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10041</v>
+        <v>10042</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>员工10041</t>
+          <t>员工10042</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14058</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="n">
-        <v>21</v>
+        <v>87</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>10042</v>
+        <v>10043</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>员工10042</t>
+          <t>员工10043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>15139</v>
-      </c>
-      <c r="E44" t="n">
-        <v>6</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>20</v>
+        <v>63</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10043</v>
+        <v>10044</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>员工10043</t>
+          <t>员工10044</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12975</v>
-      </c>
-      <c r="E45" t="n">
-        <v>7</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3</v>
-      </c>
-      <c r="G45" t="n">
-        <v>22</v>
+        <v>76</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10044</v>
+        <v>10045</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>员工10044</t>
+          <t>员工10045</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12878</v>
-      </c>
-      <c r="E46" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>22</v>
+        <v>86</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10045</v>
+        <v>10046</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>员工10045</t>
+          <t>员工10046</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12975</v>
-      </c>
-      <c r="E47" t="n">
-        <v>8</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>员工10046</t>
+          <t>员工10047</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>20802</v>
-      </c>
-      <c r="E48" t="n">
-        <v>7</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>21</v>
+        <v>82</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10047</v>
+        <v>10048</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>员工10047</t>
+          <t>员工10048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12700</v>
-      </c>
-      <c r="E49" t="n">
-        <v>8</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" t="n">
-        <v>21</v>
+        <v>69</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10048</v>
+        <v>10049</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>员工10048</t>
+          <t>员工10049</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14306</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" t="n">
-        <v>20</v>
+        <v>98</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10049</v>
+        <v>10050</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>员工10049</t>
+          <t>员工10050</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>21644</v>
-      </c>
-      <c r="E51" t="n">
-        <v>9</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>21</v>
+        <v>61</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10050</v>
+        <v>10051</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>员工10050</t>
+          <t>员工10051</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>18444</v>
-      </c>
-      <c r="E52" t="n">
-        <v>9</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="n">
-        <v>22</v>
+        <v>73</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10051</v>
+        <v>10052</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>员工10051</t>
+          <t>员工10052</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11688</v>
-      </c>
-      <c r="E53" t="n">
-        <v>6</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>21</v>
+        <v>88</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10052</v>
+        <v>10053</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>员工10052</t>
+          <t>员工10053</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>25278</v>
-      </c>
-      <c r="E54" t="n">
-        <v>13</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" t="n">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10053</v>
+        <v>10054</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>员工10053</t>
+          <t>员工10054</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11071</v>
-      </c>
-      <c r="E55" t="n">
-        <v>11</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>21</v>
+        <v>79</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10054</v>
+        <v>10055</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>员工10054</t>
+          <t>员工10055</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>100885</v>
-      </c>
-      <c r="E56" t="n">
-        <v>24</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="n">
-        <v>22</v>
+        <v>66</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10055</v>
+        <v>10056</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>员工10055</t>
+          <t>员工10056</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10106</v>
-      </c>
-      <c r="E57" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>22</v>
+        <v>94</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10056</v>
+        <v>10057</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>员工10056</t>
+          <t>员工10057</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11732</v>
-      </c>
-      <c r="E58" t="n">
-        <v>5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>3</v>
-      </c>
-      <c r="G58" t="n">
-        <v>22</v>
+        <v>76</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10057</v>
+        <v>10058</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>员工10057</t>
+          <t>员工10058</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12953</v>
-      </c>
-      <c r="E59" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>20</v>
+        <v>98</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10058</v>
+        <v>10059</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>员工10058</t>
+          <t>员工10059</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12205</v>
-      </c>
-      <c r="E60" t="n">
-        <v>4</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>22</v>
+        <v>77</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10059</v>
+        <v>10060</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>员工10059</t>
+          <t>员工10060</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10862</v>
-      </c>
-      <c r="E61" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>22</v>
+        <v>60</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10060</v>
+        <v>10061</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>员工10060</t>
+          <t>员工10061</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10330</v>
-      </c>
-      <c r="E62" t="n">
-        <v>3</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" t="n">
-        <v>21</v>
+        <v>77</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10061</v>
+        <v>10062</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>员工10061</t>
+          <t>员工10062</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14438</v>
-      </c>
-      <c r="E63" t="n">
-        <v>6</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="n">
-        <v>22</v>
+        <v>85</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10062</v>
+        <v>10063</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>员工10062</t>
+          <t>员工10063</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11660</v>
-      </c>
-      <c r="E64" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>21</v>
+        <v>64</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10063</v>
+        <v>10064</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>员工10063</t>
+          <t>员工10064</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10643</v>
-      </c>
-      <c r="E65" t="n">
-        <v>7</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>20</v>
+        <v>79</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>10064</v>
+        <v>10065</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>员工10064</t>
+          <t>员工10065</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10022</v>
-      </c>
-      <c r="E66" t="n">
-        <v>6</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>21</v>
+        <v>81</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>良好</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10065</v>
+        <v>10066</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>员工10065</t>
+          <t>员工10066</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>18201</v>
-      </c>
-      <c r="E67" t="n">
-        <v>5</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>20</v>
+        <v>79</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>10066</v>
+        <v>10067</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>员工10066</t>
+          <t>员工10067</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12214</v>
-      </c>
-      <c r="E68" t="n">
-        <v>5</v>
-      </c>
-      <c r="F68" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" t="n">
-        <v>22</v>
+        <v>61</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>10067</v>
+        <v>10068</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>员工10067</t>
+          <t>员工10068</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14470</v>
-      </c>
-      <c r="E69" t="n">
-        <v>3</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>21</v>
+        <v>96</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>10068</v>
+        <v>10069</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>员工10068</t>
+          <t>员工10069</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>19434</v>
-      </c>
-      <c r="E70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>20</v>
+        <v>74</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>10069</v>
+        <v>10070</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>员工10069</t>
+          <t>员工10070</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10882</v>
-      </c>
-      <c r="E71" t="n">
-        <v>7</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>22</v>
+        <v>98</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>10070</v>
+        <v>10071</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>员工10070</t>
+          <t>员工10071</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>17613</v>
-      </c>
-      <c r="E72" t="n">
-        <v>6</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>20</v>
+        <v>65</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>10071</v>
+        <v>10072</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>员工10071</t>
+          <t>员工10072</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15587</v>
-      </c>
-      <c r="E73" t="n">
-        <v>3</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>22</v>
+        <v>62</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>10072</v>
+        <v>10073</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>员工10072</t>
+          <t>员工10073</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>24248</v>
-      </c>
-      <c r="E74" t="n">
-        <v>14</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>22</v>
+        <v>67</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>待改进</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>10073</v>
+        <v>10074</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>员工10073</t>
+          <t>员工10074</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>销售四部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>32400</v>
-      </c>
-      <c r="E75" t="n">
-        <v>17</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>20</v>
+        <v>90</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>优秀</t>
+        </is>
       </c>
     </row>
   </sheetData>
